--- a/NguyenTrieuGiaKhanh_KeHoach_6Tuan_IOC_new.xlsx
+++ b/NguyenTrieuGiaKhanh_KeHoach_6Tuan_IOC_new.xlsx
@@ -3,18 +3,18 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4A892B-6665-4074-8D7F-1041F24FEB71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{29703254-86C0-424C-997A-42731BCBFD04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2616" yWindow="2616" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ChartData" sheetId="1" r:id="rId1"/>
+    <sheet name="ChartData" sheetId="1" state="hidden" r:id="rId1"/>
     <sheet name="Tổng quan dự án" sheetId="2" r:id="rId2"/>
     <sheet name="IOC Sân vận động PVF" sheetId="3" r:id="rId3"/>
     <sheet name="IOC Smart City" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'IOC Sân vận động PVF'!$A1:$F34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'IOC Sân vận động PVF'!$A1:$F35</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'IOC Smart City'!$A1:$F33</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Tổng quan dự án'!$A1:$E29</definedName>
   </definedNames>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="214">
   <si>
     <t>Tuần</t>
   </si>
@@ -138,7 +138,7 @@
     <t>25/05 – 31/05</t>
   </si>
   <si>
-    <t>Kickoff; BRD/SRS; prototype 6 tab; VOC–FIFA</t>
+    <t>Kickoff; BRD/SRS; prototype 6 tab; model 3D sân; VOC–FIFA</t>
   </si>
   <si>
     <t>2</t>
@@ -290,9 +290,6 @@
     <t>Dự án Vinsmartcity  |  25/05 – 14/06/2026  |  Nguyễn Triệu Gia Khánh  |  Chuẩn VOC–FIFA</t>
   </si>
   <si>
-    <t>TÓM TẮT CHO BAN LÃNH ĐẠO</t>
-  </si>
-  <si>
     <t>• Ưu tiên triển khai trước Smart City — phục vụ ban vận hành sân / an ninh sự kiện.</t>
   </si>
   <si>
@@ -320,7 +317,7 @@
     <t>Ghi chú</t>
   </si>
   <si>
-    <t>TUẦN 1 (25/05 – 31/05) — Kickoff, BRD/SRS, prototype 6 tab, căn VOC–FIFA</t>
+    <t>TUẦN 1 (25/05 – 31/05) — Kickoff, BRD/SRS, prototype 6 tab, model 3D sân, căn VOC–FIFA</t>
   </si>
   <si>
     <t>1.1</t>
@@ -359,6 +356,19 @@
     <t>1.4</t>
   </si>
   <si>
+    <t>Xây dựng model 3D sân vận động PVF</t>
+  </si>
+  <si>
+    <t>Three.js + GLB (pvf-stadium.glb): khán đài 60.000 chỗ, mái vòm, sân cỏ — phục vụ tab An ninh &amp; Tổng quan
+→ Kết quả: Model 3D sân PVF tích hợp prototype</t>
+  </si>
+  <si>
+    <t>stadium-ioc/</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
     <t>Căn thông số sân PVF</t>
   </si>
   <si>
@@ -678,6 +688,12 @@
   </si>
   <si>
     <t>Bảng số liệu, biểu đồ tổng hợp</t>
+  </si>
+  <si>
+    <t>TÓM TẮT CHUNG</t>
+  </si>
+  <si>
+    <t>Theo yêu cầu của lãnh đạo</t>
   </si>
 </sst>
 </file>
@@ -786,7 +802,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -809,11 +825,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -830,26 +874,11 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -860,32 +889,62 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1018,7 +1077,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-9B0C-44ED-A63D-0F194BCB7E69}"/>
+              <c16:uniqueId val="{00000002-4EA5-4645-A411-4566931F092C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1097,7 +1156,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-9B0C-44ED-A63D-0F194BCB7E69}"/>
+              <c16:uniqueId val="{00000003-4EA5-4645-A411-4566931F092C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1111,11 +1170,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="1969948623"/>
-        <c:axId val="1969955279"/>
+        <c:axId val="1674853343"/>
+        <c:axId val="1674853759"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1969948623"/>
+        <c:axId val="1674853343"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1125,7 +1184,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1969955279"/>
+        <c:crossAx val="1674853759"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1133,7 +1192,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1969955279"/>
+        <c:axId val="1674853759"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1144,7 +1203,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1969948623"/>
+        <c:crossAx val="1674853343"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1296,7 +1355,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-B6EB-4822-BB3E-B45DD2BEB600}"/>
+              <c16:uniqueId val="{00000002-A090-488F-8D5E-AD1566727325}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1309,11 +1368,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="1969955695"/>
-        <c:axId val="1969952783"/>
+        <c:axId val="1673153455"/>
+        <c:axId val="1673158863"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1969955695"/>
+        <c:axId val="1673153455"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1323,7 +1382,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1969952783"/>
+        <c:crossAx val="1673158863"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1331,7 +1390,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1969952783"/>
+        <c:axId val="1673158863"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1342,7 +1401,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1969955695"/>
+        <c:crossAx val="1673153455"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1463,7 +1522,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>4</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>4</c:v>
@@ -1476,7 +1535,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-897F-4627-935A-DB45A35FD44A}"/>
+              <c16:uniqueId val="{00000002-E3CC-4E55-B1E4-4C2B947330E7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1489,11 +1548,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="1969956527"/>
-        <c:axId val="1969950703"/>
+        <c:axId val="1048005759"/>
+        <c:axId val="1715907631"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1969956527"/>
+        <c:axId val="1048005759"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1503,7 +1562,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1969950703"/>
+        <c:crossAx val="1715907631"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1511,7 +1570,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1969950703"/>
+        <c:axId val="1715907631"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1522,7 +1581,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1969956527"/>
+        <c:crossAx val="1048005759"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1626,7 +1685,7 @@
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000004-4000-4597-9A25-4F282AF3594C}"/>
+                <c16:uniqueId val="{00000004-6FBB-41F3-A58B-0FA4843A5D73}"/>
               </c:ext>
             </c:extLst>
           </c:dPt>
@@ -1661,7 +1720,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-4000-4597-9A25-4F282AF3594C}"/>
+              <c16:uniqueId val="{00000002-6FBB-41F3-A58B-0FA4843A5D73}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1806,7 +1865,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-5945-42FA-85DA-CB66AD3BE788}"/>
+              <c16:uniqueId val="{00000002-6832-441A-97B7-8E55D892A7FD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1819,11 +1878,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="150"/>
-        <c:axId val="1969951535"/>
-        <c:axId val="1969959439"/>
+        <c:axId val="1715891407"/>
+        <c:axId val="1715900975"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1969951535"/>
+        <c:axId val="1715891407"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1833,7 +1892,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1969959439"/>
+        <c:crossAx val="1715900975"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1841,7 +1900,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1969959439"/>
+        <c:axId val="1715900975"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1852,7 +1911,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1969951535"/>
+        <c:crossAx val="1715891407"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1895,22 +1954,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>254000</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>340360</xdr:rowOff>
+      <xdr:colOff>93980</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>177800</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>167640</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1226820</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8A8B1B3-408D-4E67-AADB-49D423D13FA4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{009B4847-E0BD-483F-8993-4763D60F7350}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1936,14 +1995,14 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>254000</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>96520</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>5080</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>358140</xdr:colOff>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>35560</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -1951,7 +2010,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34445356-4C89-4FFF-84CF-68526A2F17EB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52FFC699-5455-49E4-8411-B735AF92A7D1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1971,23 +2030,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>259080</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>96520</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>487680</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>116840</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>35560</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F50F89D4-CCD3-473B-91C0-AE81C76297DD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C03C04AC-D5CB-4025-8A9B-039ED31A2AD5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2013,22 +2072,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>254000</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>96520</xdr:rowOff>
+      <xdr:colOff>22860</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>5080</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>426720</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>35560</xdr:rowOff>
+      <xdr:rowOff>134620</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDADC20B-52CC-441A-82BD-11151F32B171}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF8EDECE-5844-463B-BD4E-0F451FD29F64}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2048,23 +2107,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>259080</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>96520</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>548640</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>116840</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>579120</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>35560</xdr:rowOff>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED0CBC14-0634-43C7-94B1-109133C97417}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{460B4F15-8268-4411-810E-531A1BCFF861}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2465,7 +2524,7 @@
         <v>9</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2" t="s">
         <v>10</v>
@@ -2610,52 +2669,53 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="3" width="22" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
     </row>
     <row r="5" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="27" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2666,7 +2726,7 @@
       <c r="B6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="8" t="s">
         <v>35</v>
       </c>
       <c r="D6" s="13" t="s">
@@ -2681,7 +2741,7 @@
       <c r="B7" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="9" t="s">
         <v>38</v>
       </c>
       <c r="D7" s="14" t="s">
@@ -2696,7 +2756,7 @@
       <c r="B8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="8" t="s">
         <v>41</v>
       </c>
       <c r="D8" s="13" t="s">
@@ -2711,7 +2771,7 @@
       <c r="B9" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="9" t="s">
         <v>44</v>
       </c>
       <c r="D9" s="14" t="s">
@@ -2726,7 +2786,7 @@
       <c r="B10" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="8" t="s">
         <v>47</v>
       </c>
       <c r="D10" s="13" t="s">
@@ -2741,7 +2801,7 @@
       <c r="B11" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="9" t="s">
         <v>50</v>
       </c>
       <c r="D11" s="14" t="s">
@@ -2749,175 +2809,212 @@
       </c>
       <c r="E11" s="14"/>
     </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="28"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="28"/>
+    </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="28"/>
     </row>
     <row r="14" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="1" t="s">
+      <c r="C14" s="12"/>
+      <c r="D14" s="10" t="s">
         <v>55</v>
       </c>
+      <c r="E14" s="28"/>
     </row>
     <row r="15" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="2" t="s">
+      <c r="C15" s="13"/>
+      <c r="D15" s="8" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="E15" s="28"/>
+    </row>
+    <row r="16" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="4" t="s">
+      <c r="C16" s="14"/>
+      <c r="D16" s="9" t="s">
         <v>60</v>
       </c>
+      <c r="E16" s="28"/>
     </row>
     <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="2" t="s">
+      <c r="C17" s="13"/>
+      <c r="D17" s="8" t="s">
         <v>19</v>
       </c>
+      <c r="E17" s="28"/>
     </row>
     <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="17"/>
-      <c r="D18" s="4" t="s">
+      <c r="C18" s="14"/>
+      <c r="D18" s="9" t="s">
         <v>20</v>
       </c>
+      <c r="E18" s="28"/>
     </row>
     <row r="19" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="2" t="s">
+      <c r="C19" s="13"/>
+      <c r="D19" s="8" t="s">
         <v>67</v>
       </c>
+      <c r="E19" s="28"/>
     </row>
     <row r="20" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C20" s="17"/>
-      <c r="D20" s="4" t="s">
+      <c r="C20" s="14"/>
+      <c r="D20" s="9" t="s">
         <v>70</v>
       </c>
+      <c r="E20" s="28"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="28"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
     </row>
     <row r="23" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
     </row>
     <row r="24" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
     </row>
     <row r="25" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="17"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
     </row>
     <row r="26" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
     </row>
     <row r="27" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
     </row>
     <row r="28" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B27:E27"/>
@@ -2927,24 +3024,10 @@
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="D7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2953,7 +3036,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2963,96 +3046,96 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
     </row>
     <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="D10" s="12"/>
+      <c r="E10" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -3060,19 +3143,19 @@
       <c r="E11" s="19"/>
       <c r="F11" s="19"/>
     </row>
-    <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="D12" s="13"/>
+      <c r="E12" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="D12" s="13"/>
-      <c r="E12" s="8" t="s">
-        <v>100</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>9</v>
@@ -3080,17 +3163,17 @@
     </row>
     <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>103</v>
-      </c>
       <c r="D13" s="14"/>
-      <c r="E13" s="8" t="s">
-        <v>100</v>
+      <c r="E13" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>9</v>
@@ -3098,87 +3181,87 @@
     </row>
     <row r="14" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>106</v>
-      </c>
       <c r="D14" s="13"/>
-      <c r="E14" s="8" t="s">
-        <v>100</v>
+      <c r="E14" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="D15" s="14"/>
+      <c r="E15" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="D15" s="14"/>
-      <c r="E15" s="9" t="s">
+    </row>
+    <row r="16" spans="1:6" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="20" t="s">
+      <c r="C16" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-    </row>
-    <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="D16" s="13"/>
+      <c r="E16" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="F16" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C17" s="13" t="s">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+    </row>
+    <row r="18" spans="1:6" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="D18" s="14"/>
+      <c r="E18" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F18" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:6" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>120</v>
       </c>
@@ -3189,60 +3272,58 @@
         <v>122</v>
       </c>
       <c r="D19" s="13"/>
-      <c r="E19" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="F19" s="3" t="s">
+      <c r="E19" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F19" s="3"/>
+    </row>
+    <row r="20" spans="1:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="C20" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="D20" s="14"/>
+      <c r="E20" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F20" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="D20" s="14"/>
-      <c r="E20" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="F20" s="5" t="s">
+    </row>
+    <row r="21" spans="1:6" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="21" t="s">
+      <c r="B21" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B21" s="21"/>
-      <c r="C21" s="21"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
+      <c r="C21" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="D21" s="13"/>
+      <c r="E21" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C22" s="13" t="s">
+      <c r="A22" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="D22" s="13"/>
-      <c r="E22" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+    </row>
+    <row r="23" spans="1:6" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>132</v>
       </c>
@@ -3253,14 +3334,14 @@
         <v>134</v>
       </c>
       <c r="D23" s="14"/>
-      <c r="E23" s="9" t="s">
-        <v>110</v>
+      <c r="E23" s="7" t="s">
+        <v>113</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>135</v>
       </c>
@@ -3271,162 +3352,182 @@
         <v>137</v>
       </c>
       <c r="D24" s="13"/>
-      <c r="E24" s="9" t="s">
-        <v>110</v>
+      <c r="E24" s="7" t="s">
+        <v>113</v>
       </c>
       <c r="F24" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="12" t="s">
+      <c r="B25" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-    </row>
-    <row r="27" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
+      <c r="C25" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="D25" s="14"/>
+      <c r="E25" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+    </row>
+    <row r="28" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C27" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="D27" s="15"/>
-      <c r="E27" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+      <c r="C28" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="D28" s="12"/>
+      <c r="E28" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="D28" s="13"/>
-      <c r="E28" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
+      <c r="C29" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="D29" s="13"/>
+      <c r="E29" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B30" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="D29" s="14"/>
-      <c r="E29" s="5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+      <c r="C30" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="D30" s="14"/>
+      <c r="E30" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B31" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="D30" s="13"/>
-      <c r="E30" s="3" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
+      <c r="C31" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="D31" s="13"/>
+      <c r="E31" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="D31" s="14"/>
-      <c r="E31" s="5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+      <c r="B32" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="D32" s="14"/>
+      <c r="E32" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B33" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C32" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="D32" s="13"/>
-      <c r="E32" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="4" t="s">
+      <c r="C33" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="D33" s="13"/>
+      <c r="E33" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B34" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C33" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="D33" s="14"/>
-      <c r="E33" s="5" t="s">
-        <v>155</v>
+      <c r="C34" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="D34" s="14"/>
+      <c r="E34" s="5" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="31">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C34:D34"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3445,96 +3546,96 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
+      <c r="A1" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
+      <c r="A2" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
+      <c r="A4" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
+      <c r="A5" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
+      <c r="A6" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
+      <c r="A7" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="18" t="s">
-        <v>161</v>
-      </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
+      <c r="A8" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
     </row>
     <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="D10" s="12"/>
+      <c r="E10" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="22" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B11" s="22"/>
       <c r="C11" s="22"/>
@@ -3542,19 +3643,19 @@
       <c r="E11" s="22"/>
       <c r="F11" s="22"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D12" s="13"/>
-      <c r="E12" s="9" t="s">
-        <v>110</v>
+      <c r="E12" s="7" t="s">
+        <v>113</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>11</v>
@@ -3562,163 +3663,163 @@
     </row>
     <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D13" s="14"/>
-      <c r="E13" s="9" t="s">
-        <v>110</v>
+      <c r="E13" s="7" t="s">
+        <v>113</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D14" s="13"/>
-      <c r="E14" s="9" t="s">
-        <v>110</v>
+      <c r="E14" s="7" t="s">
+        <v>113</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="23" t="s">
-        <v>173</v>
-      </c>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="B15" s="21"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+    </row>
+    <row r="16" spans="1:6" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D16" s="14"/>
-      <c r="E16" s="9" t="s">
-        <v>110</v>
+      <c r="E16" s="7" t="s">
+        <v>113</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D17" s="13"/>
-      <c r="E17" s="9" t="s">
-        <v>110</v>
+      <c r="E17" s="7" t="s">
+        <v>113</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D18" s="14"/>
-      <c r="E18" s="9" t="s">
-        <v>110</v>
+      <c r="E18" s="7" t="s">
+        <v>113</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D19" s="13"/>
-      <c r="E19" s="9" t="s">
-        <v>110</v>
+      <c r="E19" s="7" t="s">
+        <v>113</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="24" t="s">
-        <v>187</v>
-      </c>
-      <c r="B20" s="24"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+    </row>
+    <row r="21" spans="1:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D21" s="14"/>
-      <c r="E21" s="9" t="s">
-        <v>110</v>
+      <c r="E21" s="7" t="s">
+        <v>113</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D22" s="13"/>
-      <c r="E22" s="9" t="s">
-        <v>110</v>
+      <c r="E22" s="7" t="s">
+        <v>113</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>20</v>
@@ -3726,47 +3827,47 @@
     </row>
     <row r="23" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D23" s="14"/>
-      <c r="E23" s="9" t="s">
-        <v>110</v>
+      <c r="E23" s="7" t="s">
+        <v>113</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
+      <c r="A25" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
     </row>
     <row r="26" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C26" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="D26" s="15"/>
+      <c r="C26" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="D26" s="12"/>
       <c r="E26" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>34</v>
       </c>
@@ -3774,7 +3875,7 @@
         <v>8</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D27" s="13"/>
       <c r="E27" s="3" t="s">
@@ -3786,14 +3887,14 @@
         <v>37</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D28" s="14"/>
       <c r="E28" s="5" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3804,11 +3905,11 @@
         <v>13</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D29" s="13"/>
       <c r="E29" s="3" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -3816,25 +3917,25 @@
         <v>43</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D31" s="13"/>
       <c r="E31" s="3" t="s">
@@ -3849,7 +3950,7 @@
         <v>26</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D32" s="14"/>
       <c r="E32" s="5" t="s">
@@ -3858,6 +3959,26 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="C31:D31"/>
@@ -3867,28 +3988,9 @@
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/NguyenTrieuGiaKhanh_KeHoach_6Tuan_IOC_new.xlsx
+++ b/NguyenTrieuGiaKhanh_KeHoach_6Tuan_IOC_new.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{29703254-86C0-424C-997A-42731BCBFD04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{89A76074-B231-495C-8638-D56E9F5FE141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="217">
   <si>
     <t>Tuần</t>
   </si>
@@ -359,10 +359,6 @@
     <t>Xây dựng model 3D sân vận động PVF</t>
   </si>
   <si>
-    <t>Three.js + GLB (pvf-stadium.glb): khán đài 60.000 chỗ, mái vòm, sân cỏ — phục vụ tab An ninh &amp; Tổng quan
-→ Kết quả: Model 3D sân PVF tích hợp prototype</t>
-  </si>
-  <si>
     <t>stadium-ioc/</t>
   </si>
   <si>
@@ -694,6 +690,19 @@
   </si>
   <si>
     <t>Theo yêu cầu của lãnh đạo</t>
+  </si>
+  <si>
+    <t>4,2</t>
+  </si>
+  <si>
+    <t>Xây dựng model 3D cho 4 tab vận hành Smart City (Giao thông · An ninh · Môi trường · Tiện ích)</t>
+  </si>
+  <si>
+    <t>Xây dựng scene Three.js cho Giao thông, An ninh, Môi trường, Tiện ích — mỗi tab có model 3D + HUD hai bên → Kết quả: 4 tab Smart City có mô hình 3D tương tác hoàn chỉnh</t>
+  </si>
+  <si>
+    <t>Three.js + GLB (pvf-stadium.glb): khán đài 60.000 chỗ, mái vòm, sân cỏ — phục vụ tab An ninh, Tổng quan, sự kiện, cơ sở hạ tầng và dịch vụ
+→ Kết quả: Model 3D sân PVF tích hợp prototype</t>
   </si>
 </sst>
 </file>
@@ -802,7 +811,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -853,11 +862,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -945,6 +980,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2073,13 +2114,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>60960</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>426720</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>134620</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2109,13 +2150,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>548640</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>579120</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2719,7 +2760,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
@@ -2734,7 +2775,7 @@
       </c>
       <c r="E6" s="13"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>1</v>
       </c>
@@ -2749,7 +2790,7 @@
       </c>
       <c r="E7" s="14"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
@@ -2764,7 +2805,7 @@
       </c>
       <c r="E8" s="13"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>2</v>
       </c>
@@ -2779,7 +2820,7 @@
       </c>
       <c r="E9" s="14"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>2</v>
       </c>
@@ -2794,7 +2835,7 @@
       </c>
       <c r="E10" s="13"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>2</v>
       </c>
@@ -3067,7 +3108,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="29" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B4" s="29"/>
       <c r="C4" s="29"/>
@@ -3197,7 +3238,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>106</v>
       </c>
@@ -3205,37 +3246,37 @@
         <v>107</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>108</v>
+        <v>216</v>
       </c>
       <c r="D15" s="14"/>
       <c r="E15" s="6" t="s">
         <v>99</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="13" t="s">
         <v>111</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>112</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>113</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B17" s="18"/>
       <c r="C17" s="18"/>
@@ -3245,77 +3286,77 @@
     </row>
     <row r="18" spans="1:6" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="14" t="s">
         <v>117</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>118</v>
       </c>
       <c r="D18" s="14"/>
       <c r="E18" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C19" s="13" t="s">
         <v>121</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>122</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F19" s="3"/>
     </row>
     <row r="20" spans="1:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="C20" s="14" t="s">
         <v>124</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>125</v>
       </c>
       <c r="D20" s="14"/>
       <c r="E20" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="13" t="s">
         <v>128</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>129</v>
       </c>
       <c r="D21" s="13"/>
       <c r="E21" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="17" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
@@ -3325,17 +3366,17 @@
     </row>
     <row r="23" spans="1:6" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="C23" s="14" t="s">
         <v>133</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>134</v>
       </c>
       <c r="D23" s="14"/>
       <c r="E23" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>19</v>
@@ -3343,17 +3384,17 @@
     </row>
     <row r="24" spans="1:6" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="13" t="s">
         <v>136</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>137</v>
       </c>
       <c r="D24" s="13"/>
       <c r="E24" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>19</v>
@@ -3361,25 +3402,25 @@
     </row>
     <row r="25" spans="1:6" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="C25" s="14" t="s">
         <v>139</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>140</v>
       </c>
       <c r="D25" s="14"/>
       <c r="E25" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
@@ -3388,17 +3429,17 @@
     </row>
     <row r="28" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D28" s="12"/>
       <c r="E28" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3409,11 +3450,11 @@
         <v>8</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D29" s="13"/>
       <c r="E29" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3424,11 +3465,11 @@
         <v>13</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3439,11 +3480,11 @@
         <v>18</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D31" s="13"/>
       <c r="E31" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3451,14 +3492,14 @@
         <v>43</v>
       </c>
       <c r="B32" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C32" s="14" t="s">
         <v>152</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>153</v>
       </c>
       <c r="D32" s="14"/>
       <c r="E32" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -3469,11 +3510,11 @@
         <v>24</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D33" s="13"/>
       <c r="E33" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -3484,11 +3525,11 @@
         <v>26</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D34" s="14"/>
       <c r="E34" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -3536,7 +3577,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -3547,7 +3588,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3557,7 +3598,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
@@ -3567,7 +3608,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="23" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B4" s="23"/>
       <c r="C4" s="23"/>
@@ -3577,7 +3618,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B5" s="24"/>
       <c r="C5" s="24"/>
@@ -3587,7 +3628,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="24" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B6" s="24"/>
       <c r="C6" s="24"/>
@@ -3597,7 +3638,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="24" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B7" s="24"/>
       <c r="C7" s="24"/>
@@ -3607,7 +3648,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B8" s="24"/>
       <c r="C8" s="24"/>
@@ -3635,7 +3676,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="22" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B11" s="22"/>
       <c r="C11" s="22"/>
@@ -3645,320 +3686,337 @@
     </row>
     <row r="12" spans="1:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="13" t="s">
         <v>167</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>168</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:6" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="D13" s="31"/>
+      <c r="E13" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F13" s="8"/>
+    </row>
+    <row r="14" spans="1:6" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C14" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="D14" s="14"/>
+      <c r="E14" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="D13" s="14"/>
-      <c r="E13" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F13" s="5" t="s">
+    </row>
+    <row r="15" spans="1:6" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C15" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="D15" s="13"/>
+      <c r="E15" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="21" t="s">
         <v>175</v>
       </c>
-      <c r="D14" s="13"/>
-      <c r="E14" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="21" t="s">
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+    </row>
+    <row r="17" spans="1:6" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="21"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="21"/>
-    </row>
-    <row r="16" spans="1:6" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C17" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="D17" s="14"/>
+      <c r="E17" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D16" s="14"/>
-      <c r="E16" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F16" s="5" t="s">
+      <c r="B18" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="D18" s="13"/>
+      <c r="E18" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C17" s="13" t="s">
+    <row r="19" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C19" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="D19" s="14"/>
+      <c r="E19" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F18" s="5" t="s">
+    </row>
+    <row r="20" spans="1:6" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="C20" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="D20" s="13"/>
+      <c r="E20" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="D19" s="13"/>
-      <c r="E19" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="20" t="s">
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+    </row>
+    <row r="22" spans="1:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-    </row>
-    <row r="21" spans="1:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="C22" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="D22" s="14"/>
+      <c r="E22" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="D21" s="14"/>
-      <c r="E21" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F21" s="5" t="s">
+      <c r="B23" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="D23" s="13"/>
+      <c r="E23" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C22" s="13" t="s">
+    <row r="24" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="D22" s="13"/>
-      <c r="E22" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
+      <c r="B24" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="C24" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="D24" s="14"/>
+      <c r="E24" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F24" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="D23" s="14"/>
-      <c r="E23" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="F23" s="5" t="s">
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="11" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="11" t="s">
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+    </row>
+    <row r="27" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="D27" s="12"/>
+      <c r="E27" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-    </row>
-    <row r="26" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="D26" s="12"/>
-      <c r="E26" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="13" t="s">
+      <c r="D28" s="13"/>
+      <c r="E28" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="D27" s="13"/>
-      <c r="E27" s="3" t="s">
+      <c r="C29" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="D29" s="14"/>
+      <c r="E29" s="5" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="D30" s="13"/>
+      <c r="E30" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="D31" s="14"/>
+      <c r="E31" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="D28" s="14"/>
-      <c r="E28" s="5" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="D29" s="13"/>
-      <c r="E29" s="3" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="C30" s="14" t="s">
+    <row r="32" spans="1:6" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="D30" s="14"/>
-      <c r="E30" s="5" t="s">
+      <c r="C32" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="D32" s="13"/>
+      <c r="E32" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C31" s="13" t="s">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="D31" s="13"/>
-      <c r="E31" s="3" t="s">
+      <c r="D33" s="14"/>
+      <c r="E33" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="D32" s="14"/>
-      <c r="E32" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="30">
+    <mergeCell ref="C13:D13"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
@@ -3969,25 +4027,25 @@
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
     <mergeCell ref="C14:D14"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A16:F16"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="A21:F21"/>
     <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C23:D23"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="A26:E26"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/NguyenTrieuGiaKhanh_KeHoach_6Tuan_IOC_new.xlsx
+++ b/NguyenTrieuGiaKhanh_KeHoach_6Tuan_IOC_new.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{89A76074-B231-495C-8638-D56E9F5FE141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6BCA8E8-9998-4CAA-AEF5-2F109EDD2D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ChartData" sheetId="1" state="hidden" r:id="rId1"/>
@@ -18,8 +18,17 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">'IOC Smart City'!$A1:$F33</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Tổng quan dự án'!$A1:$E29</definedName>
   </definedNames>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -28,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="223">
   <si>
     <t>Tuần</t>
   </si>
@@ -339,18 +348,10 @@
     <t>Soạn BRD/SRS PVF</t>
   </si>
   <si>
-    <t>Ghi rõ 60.000 chỗ, mái vòm, yêu cầu VOC–FIFA
-→ Kết quả: BRD/SRS bản 1</t>
-  </si>
-  <si>
     <t>1.3</t>
   </si>
   <si>
     <t>Branding &amp; prototype 6 tab</t>
-  </si>
-  <si>
-    <t>stadium-ioc/ — 6 tab venue
-→ Kết quả: Prototype xem trước demo VOC</t>
   </si>
   <si>
     <t>1.4</t>
@@ -400,10 +401,6 @@
     <t>Tài liệu kiến trúc PVF</t>
   </si>
   <si>
-    <t>Dual IOC + điểm tích hợp VOC (camera, BMS, ticketing…)
-→ Kết quả: Kiến trúc bản 1</t>
-  </si>
-  <si>
     <t>2.3</t>
   </si>
   <si>
@@ -703,6 +700,36 @@
   <si>
     <t>Three.js + GLB (pvf-stadium.glb): khán đài 60.000 chỗ, mái vòm, sân cỏ — phục vụ tab An ninh, Tổng quan, sự kiện, cơ sở hạ tầng và dịch vụ
 → Kết quả: Model 3D sân PVF tích hợp prototype</t>
+  </si>
+  <si>
+    <t>Hạ tầng: đóng/mở mái 12–20 phút; An ninh/Sự kiện/Dịch vụ: 1 kịch bản chéo (mật độ B → timeline → bãi/F&amp;B); kiểm thử nội bộ 5 tab. → Kết quả: Demo closed-loop 1 trận; kiến trúc VOC bản 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Báo cáo tổng hợp KPI 4 phân hệ + UAT PVF</t>
+  </si>
+  <si>
+    <t>Tab Báo cáo gom KPI An ninh/Sự kiện/Hạ tầng/Dịch vụ; đồng bộ số liệu 1 kịch bản; checklist UAT 5 phòng → ký nghiệm thu PVF. → Kết quả: Gói PVF hoàn thành (prototype + tài liệu).</t>
+  </si>
+  <si>
+    <t>Thiết lập 5 tab vận hành (An ninh · Sự kiện · Hạ tầng · Dịch vụ · Báo cáo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mỗi tab vận hành theo từng phòng ban và chức năng của phòng đó: HUD + KPI + cảnh báo demo trên 3D PVF; ghi phạm vi từng phòng trong BRD/SRS. → Kết quả: 5 tab có dữ liệu mock, đọc được trên phòng điều hành.
+</t>
+  </si>
+  <si>
+    <t>Soạn BRD/SRS PVF bản 1 — Sức chứa 60.000 chỗ; 3D mô phỏng 2.000–3.000 ghế đại diện, KPI tính theo % lấp đầy (vd. 80% → 48.000 khán giả); mô phỏng mái vòm PTFE (12–20 phút); căn VOC–FIFA trên 5 phân hệ.</t>
+  </si>
+  <si>
+    <t>Thiết kế giao diện PVF và dựng trang web demo 6 tab (Tổng quan, An ninh, Sự kiện, Cơ sở hạ tầng, Dịch vụ, Báo cáo) tại stadium-ioc/ — dữ liệu mẫu, chưa nối hệ thống thật.
+→ Kết quả: Prototype demo phòng điều hành sân (VOC) để trình lãnh đạo xem trước.</t>
+  </si>
+  <si>
+    <t>Xây dựng kiến trúc hệ thống PVF: IOC sân liên kết Smart City; thiết lập cấu trúc module và điểm tích hợp VOC (camera, BMS mái/HVAC, vé điện tử) — prototype dùng dữ liệu mẫu, có thể nối hệ thống thật sau.
+→ Kết quả: Kiến trúc bản 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Hoàn thiện luồng vận hành 5 phòng + mô phỏng mái vòm</t>
   </si>
 </sst>
 </file>
@@ -811,7 +838,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -888,11 +915,79 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -942,12 +1037,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -986,6 +1075,81 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2037,13 +2201,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>60960</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>358140</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>35560</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2073,13 +2237,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>487680</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>60960</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>51</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2149,15 +2313,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>548640</xdr:colOff>
+      <xdr:colOff>579120</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>579120</xdr:colOff>
+      <xdr:colOff>243840</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
+      <xdr:rowOff>142240</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2735,28 +2899,28 @@
       <c r="E2" s="16"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
     </row>
     <row r="5" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="25" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2851,20 +3015,20 @@
       <c r="E11" s="14"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="28"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28"/>
+      <c r="A12" s="26"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="25"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="28"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="26"/>
     </row>
     <row r="14" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
@@ -2877,7 +3041,7 @@
       <c r="D14" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="28"/>
+      <c r="E14" s="26"/>
     </row>
     <row r="15" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
@@ -2890,7 +3054,7 @@
       <c r="D15" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="28"/>
+      <c r="E15" s="26"/>
     </row>
     <row r="16" spans="1:5" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
@@ -2903,7 +3067,7 @@
       <c r="D16" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E16" s="28"/>
+      <c r="E16" s="26"/>
     </row>
     <row r="17" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
@@ -2916,7 +3080,7 @@
       <c r="D17" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="28"/>
+      <c r="E17" s="26"/>
     </row>
     <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
@@ -2929,7 +3093,7 @@
       <c r="D18" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="28"/>
+      <c r="E18" s="26"/>
     </row>
     <row r="19" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
@@ -2942,7 +3106,7 @@
       <c r="D19" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="E19" s="28"/>
+      <c r="E19" s="26"/>
     </row>
     <row r="20" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
@@ -2955,23 +3119,23 @@
       <c r="D20" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="E20" s="28"/>
+      <c r="E20" s="26"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="28"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
+      <c r="A21" s="26"/>
+      <c r="B21" s="26"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="26" t="s">
+      <c r="A22" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="B22" s="26"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
     </row>
     <row r="23" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
@@ -3077,7 +3241,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -3107,54 +3271,54 @@
       <c r="F2" s="16"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="29" t="s">
-        <v>211</v>
-      </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
+      <c r="A4" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="B4" s="27"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="B8" s="24"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
     </row>
     <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
@@ -3175,14 +3339,14 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
     </row>
     <row r="12" spans="1:6" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
@@ -3202,7 +3366,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="76.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>100</v>
       </c>
@@ -3210,7 +3374,7 @@
         <v>101</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>102</v>
+        <v>219</v>
       </c>
       <c r="D13" s="14"/>
       <c r="E13" s="6" t="s">
@@ -3220,15 +3384,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="93.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="C14" s="13" t="s">
-        <v>105</v>
+        <v>220</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="6" t="s">
@@ -3240,300 +3404,353 @@
     </row>
     <row r="15" spans="1:6" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D15" s="14"/>
       <c r="E15" s="6" t="s">
         <v>99</v>
       </c>
       <c r="F15" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="33" t="s">
+        <v>107</v>
+      </c>
+      <c r="B16" s="34" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="C16" s="35" t="s">
         <v>109</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="D16" s="35"/>
+      <c r="E16" s="36" t="s">
         <v>110</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="F16" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="7" t="s">
+    </row>
+    <row r="17" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="40">
+        <v>1.6</v>
+      </c>
+      <c r="B17" s="41" t="s">
+        <v>217</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>218</v>
+      </c>
+      <c r="D17" s="42"/>
+      <c r="E17" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="F17" s="41"/>
+    </row>
+    <row r="18" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="37" t="s">
         <v>112</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="39"/>
+    </row>
+    <row r="19" spans="1:6" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="18" t="s">
+      <c r="B19" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-    </row>
-    <row r="18" spans="1:6" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="C19" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="D19" s="14"/>
+      <c r="E19" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F19" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C18" s="14" t="s">
+    </row>
+    <row r="20" spans="1:6" ht="91.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="F18" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="C20" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="D20" s="13"/>
+      <c r="E20" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F20" s="3"/>
+    </row>
+    <row r="21" spans="1:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C21" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="D19" s="13"/>
-      <c r="E19" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="F19" s="3"/>
-    </row>
-    <row r="20" spans="1:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
+      <c r="D21" s="14"/>
+      <c r="E21" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F21" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="B20" s="5" t="s">
+    </row>
+    <row r="22" spans="1:6" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="B22" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D20" s="14"/>
-      <c r="E20" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="F20" s="5" t="s">
+      <c r="C22" s="13" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B21" s="3" t="s">
+      <c r="D22" s="13"/>
+      <c r="E22" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="B23" s="31"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="32"/>
+    </row>
+    <row r="24" spans="1:6" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="D21" s="13"/>
-      <c r="E21" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="17" t="s">
+      <c r="B24" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C24" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-    </row>
-    <row r="23" spans="1:6" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
+      <c r="D24" s="14"/>
+      <c r="E24" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="C25" s="53" t="s">
+        <v>216</v>
+      </c>
+      <c r="D25" s="54"/>
+      <c r="E25" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F25" s="9"/>
+    </row>
+    <row r="26" spans="1:6" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C26" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="D23" s="14"/>
-      <c r="E23" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="F23" s="5" t="s">
+      <c r="D26" s="13"/>
+      <c r="E26" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+    <row r="27" spans="1:6" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="43" t="s">
         <v>134</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B27" s="44" t="s">
         <v>135</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C27" s="45" t="s">
         <v>136</v>
       </c>
-      <c r="D24" s="13"/>
-      <c r="E24" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
+      <c r="D27" s="45"/>
+      <c r="E27" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="F27" s="44" t="s">
         <v>137</v>
       </c>
-      <c r="B25" s="5" t="s">
+    </row>
+    <row r="28" spans="1:6" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="49">
+        <v>3.4</v>
+      </c>
+      <c r="B28" s="50" t="s">
+        <v>222</v>
+      </c>
+      <c r="C28" s="51" t="s">
+        <v>214</v>
+      </c>
+      <c r="D28" s="52"/>
+      <c r="E28" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="F28" s="50"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="46" t="s">
         <v>138</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="B29" s="47"/>
+      <c r="C29" s="47"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="48"/>
+    </row>
+    <row r="30" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D25" s="14"/>
-      <c r="E25" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="F25" s="5" t="s">
+      <c r="B30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30" s="12" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="11" t="s">
+      <c r="D30" s="12"/>
+      <c r="E30" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-    </row>
-    <row r="28" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="D28" s="12"/>
-      <c r="E28" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="D29" s="13"/>
-      <c r="E29" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="D30" s="14"/>
-      <c r="E30" s="5" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D31" s="13"/>
       <c r="E31" s="3" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>151</v>
+        <v>13</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="D32" s="14"/>
       <c r="E32" s="5" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D33" s="13"/>
       <c r="E33" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>26</v>
+        <v>148</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D34" s="14"/>
       <c r="E34" s="5" t="s">
-        <v>157</v>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="D35" s="13"/>
+      <c r="E35" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="D36" s="14"/>
+      <c r="E36" s="5" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="34">
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C25:D25"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
@@ -3548,23 +3765,21 @@
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="C18:D18"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C22:D22"/>
     <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="A29:E29"/>
     <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C36:D36"/>
     <mergeCell ref="C31:D31"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3588,7 +3803,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3598,7 +3813,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B2" s="16"/>
       <c r="C2" s="16"/>
@@ -3607,54 +3822,54 @@
       <c r="F2" s="16"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="23" t="s">
-        <v>211</v>
-      </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
+      <c r="A4" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="24" t="s">
-        <v>162</v>
-      </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="24" t="s">
-        <v>163</v>
-      </c>
-      <c r="B8" s="24"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
     </row>
     <row r="10" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
@@ -3675,28 +3890,28 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
+      <c r="A11" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
     </row>
     <row r="12" spans="1:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>11</v>
@@ -3704,79 +3919,79 @@
     </row>
     <row r="13" spans="1:6" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="C13" s="30" t="s">
-        <v>215</v>
-      </c>
-      <c r="D13" s="31"/>
+        <v>211</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>212</v>
+      </c>
+      <c r="D13" s="29"/>
       <c r="E13" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F13" s="8"/>
     </row>
     <row r="14" spans="1:6" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D14" s="14"/>
       <c r="E14" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
+      <c r="A16" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
     </row>
     <row r="17" spans="1:6" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D17" s="14"/>
       <c r="E17" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>16</v>
@@ -3784,17 +3999,17 @@
     </row>
     <row r="18" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>16</v>
@@ -3802,63 +4017,63 @@
     </row>
     <row r="19" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D19" s="14"/>
       <c r="E19" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D20" s="13"/>
       <c r="E20" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
+      <c r="A21" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
     </row>
     <row r="22" spans="1:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>20</v>
@@ -3866,17 +4081,17 @@
     </row>
     <row r="23" spans="1:6" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D23" s="13"/>
       <c r="E23" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>20</v>
@@ -3884,25 +4099,25 @@
     </row>
     <row r="24" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="11" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -3911,13 +4126,13 @@
     </row>
     <row r="27" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D27" s="12"/>
       <c r="E27" s="1" t="s">
@@ -3932,7 +4147,7 @@
         <v>8</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D28" s="13"/>
       <c r="E28" s="3" t="s">
@@ -3944,14 +4159,14 @@
         <v>37</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D29" s="14"/>
       <c r="E29" s="5" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
@@ -3962,11 +4177,11 @@
         <v>13</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D30" s="13"/>
       <c r="E30" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -3974,10 +4189,10 @@
         <v>43</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D31" s="14"/>
       <c r="E31" s="5" t="s">
@@ -3989,10 +4204,10 @@
         <v>46</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D32" s="13"/>
       <c r="E32" s="3" t="s">
@@ -4007,7 +4222,7 @@
         <v>26</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D33" s="14"/>
       <c r="E33" s="5" t="s">
